--- a/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Rajasthan/results/SoIB_summaries.xlsx
@@ -512,10 +512,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>28.1</v>
       </c>
       <c r="E2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -523,16 +523,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>22.6</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -543,13 +543,13 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="E4">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -591,10 +591,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C8">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -756,7 +756,7 @@
         <v>67</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +764,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -813,7 +813,7 @@
         <v>74</v>
       </c>
       <c r="C2">
-        <v>69.8</v>
+        <v>69.2</v>
       </c>
       <c r="D2">
         <v>73</v>
@@ -844,10 +844,10 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>18</v>
